--- a/owlcms/src/main/resources/templates/protocol/PanAm3Medals-A4.xlsx
+++ b/owlcms/src/main/resources/templates/protocol/PanAm3Medals-A4.xlsx
@@ -484,7 +484,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns5="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" ns1:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns5="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="_-#,##0;[Red]\(#,##0\);\-"/>
     <numFmt numFmtId="165" formatCode="0;\(0\);\-"/>
@@ -2793,7 +2793,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns2:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Feuil4">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>

--- a/owlcms/src/main/resources/templates/protocol/PanAm3Medals-A4.xlsx
+++ b/owlcms/src/main/resources/templates/protocol/PanAm3Medals-A4.xlsx
@@ -123,7 +123,7 @@
             <rFont val="Tahoma"/>
             <charset val="1"/>
           </rPr>
-          <t>jx:if(condition="records != null" lastCell="V15")</t>
+          <t>jx:if(condition="session.records.size() &gt; 0" lastCell="V15")</t>
         </r>
       </text>
     </comment>
@@ -147,7 +147,7 @@
             <charset val="1"/>
           </rPr>
           <t xml:space="preserve">
-jx:each(items="records" var="r" lastCell="V15")</t>
+jx:each(items="session.records" var="r" lastCell="V15")</t>
         </r>
       </text>
     </comment>
@@ -484,14 +484,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns5="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="_-#,##0;[Red]\(#,##0\);\-"/>
     <numFmt numFmtId="165" formatCode="0;\(0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.000;;\-"/>
     <numFmt numFmtId="167" formatCode="_-#,##0;[Red]\(#,##0\);\-"/>
   </numFmts>
-  <fonts count="79" ns2:knownFonts="1">
+  <fonts count="171" ns1:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -951,6 +951,571 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
   </fonts>
   <fills count="59">
     <fill>
@@ -1169,7 +1734,7 @@
       <patternFill patternType="none"/>
     </fill>
   </fills>
-  <borders count="74">
+  <borders count="164">
     <border>
       <left/>
       <right/>
@@ -1859,6 +2424,660 @@
       <top/>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
     </border>
   </borders>
   <cellStyleXfs count="19">
@@ -1882,7 +3101,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="161">
+  <cellXfs count="262">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2326,6 +3545,328 @@
     <xf numFmtId="0" fontId="78" fillId="58" borderId="73" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="74" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="75" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="76" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="77" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="78" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="79" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="80" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="81" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="82" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="86" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="87" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="88" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="89" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="90" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="91" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="92" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="93" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="94" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="100" fillId="0" borderId="95" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1" applyAlignment="1">
+      <protection locked="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="101" fillId="0" borderId="96" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1" applyAlignment="1">
+      <protection locked="0"/>
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="102" fillId="0" borderId="97" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1" applyAlignment="1">
+      <protection locked="0"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="98" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="99" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="100" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="106" fillId="0" borderId="101" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="107" fillId="0" borderId="102" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="108" fillId="0" borderId="103" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="104" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="105" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="106" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="107" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="108" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="109" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="110" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="111" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="112" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="0" borderId="113" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="114" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="120" fillId="0" borderId="115" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="117" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="118" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="119" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="120" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="0" borderId="121" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="0" borderId="122" xfId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="0" borderId="123" xfId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="129" fillId="0" borderId="124" xfId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="130" fillId="0" borderId="125" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="131" fillId="0" borderId="126" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="132" fillId="0" borderId="127" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="133" fillId="0" borderId="128" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="134" fillId="0" borderId="129" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="135" fillId="0" borderId="130" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="136" fillId="0" borderId="131" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="132" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="133" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="0" borderId="134" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="140" fillId="0" borderId="135" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="0" borderId="136" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="142" fillId="0" borderId="137" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="143" fillId="0" borderId="138" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="144" fillId="0" borderId="139" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="145" fillId="0" borderId="140" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="146" fillId="0" borderId="141" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="147" fillId="0" borderId="142" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="148" fillId="0" borderId="143" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="149" fillId="0" borderId="144" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="150" fillId="0" borderId="145" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="151" fillId="0" borderId="146" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="152" fillId="0" borderId="147" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="153" fillId="0" borderId="148" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="154" fillId="0" borderId="149" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="155" fillId="0" borderId="150" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="156" fillId="0" borderId="151" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="157" fillId="0" borderId="152" xfId="0" applyProtection="1" applyAlignment="1">
+      <protection locked="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="158" fillId="0" borderId="153" xfId="0" applyProtection="1" applyAlignment="1">
+      <protection locked="0"/>
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="159" fillId="0" borderId="154" xfId="0" applyProtection="1" applyAlignment="1">
+      <protection locked="0"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="160" fillId="0" borderId="155" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="161" fillId="0" borderId="156" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="162" fillId="0" borderId="157" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="163" fillId="0" borderId="158" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="164" fillId="0" borderId="159" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="165" fillId="0" borderId="160" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="166" fillId="0" borderId="161" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="167" fillId="0" borderId="162" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="168" fillId="0" borderId="163" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="107" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyBorder="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="134" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="135" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="146" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="150" fillId="0" borderId="0" xfId="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="169" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="170" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="0" applyAlignment="1" applyProtection="1" applyFont="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="19">
     <cellStyle name="Accent1" xfId="1" builtinId="29" customBuiltin="1"/>
@@ -2334,18 +3875,18 @@
     <cellStyle name="Accent4" xfId="4" builtinId="41" customBuiltin="1"/>
     <cellStyle name="Accent5" xfId="5" builtinId="45" customBuiltin="1"/>
     <cellStyle name="Accent6" xfId="6" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Emphase 1" xfId="7" ns3:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="Emphase 2" xfId="8" ns3:uid="{00000000-0005-0000-0000-000007000000}"/>
-    <cellStyle name="Emphase 3" xfId="9" ns3:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="Emphase 1" xfId="7" ns2:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Emphase 2" xfId="8" ns2:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="Emphase 3" xfId="9" ns2:uid="{00000000-0005-0000-0000-000008000000}"/>
     <cellStyle name="Hyperlink" xfId="10" builtinId="8"/>
-    <cellStyle name="Lien hypertexte 2" xfId="11" ns3:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="Lien hypertexte 2" xfId="11" ns2:uid="{00000000-0005-0000-0000-00000A000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="12" ns3:uid="{00000000-0005-0000-0000-00000C000000}"/>
-    <cellStyle name="Normal 3" xfId="13" ns3:uid="{00000000-0005-0000-0000-00000D000000}"/>
-    <cellStyle name="Titre 1" xfId="14" ns3:uid="{00000000-0005-0000-0000-00000E000000}"/>
-    <cellStyle name="Titre 1 1" xfId="15" ns3:uid="{00000000-0005-0000-0000-00000F000000}"/>
-    <cellStyle name="Titre 1 1 1" xfId="16" ns3:uid="{00000000-0005-0000-0000-000010000000}"/>
-    <cellStyle name="Titre de la feuille" xfId="17" ns3:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="Normal 2" xfId="12" ns2:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="Normal 3" xfId="13" ns2:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="Titre 1" xfId="14" ns2:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="Titre 1 1" xfId="15" ns2:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="Titre 1 1 1" xfId="16" ns2:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="Titre de la feuille" xfId="17" ns2:uid="{00000000-0005-0000-0000-000011000000}"/>
     <cellStyle name="Total" xfId="18" builtinId="25" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="2">
@@ -2437,10 +3978,10 @@
   </colors>
   <extLst>
     <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <ns4:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+      <ns3:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
     <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <ns5:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+      <ns4:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2793,12 +4334,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns2:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns3="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Feuil4">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X101"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" ns3:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" ns2:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" customWidth="1"/>
     <col min="2" max="2" width="5.42578125" style="1" customWidth="1"/>
@@ -2822,116 +4363,71 @@
     <col min="25" max="25" width="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="H1" s="116" t="s">
-        <v>16</v>
-      </c>
-      <c r="I1" s="116"/>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
-      <c r="V1" s="116"/>
-    </row>
-    <row r="2" spans="1:24" ht="19.5" customHeight="1" ns3:dyDescent="0.2">
-      <c r="A2" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="4"/>
-      <c r="G2" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="H2" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" s="113"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="22"/>
-      <c r="N2" s="23"/>
-      <c r="O2" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="P2" s="114" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q2" s="115"/>
-      <c r="R2" s="115"/>
-      <c r="S2" s="1"/>
-    </row>
-    <row r="3" spans="1:24" ht="19.5" customHeight="1" ns3:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="25"/>
-      <c r="G3" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" s="39" t="s">
-        <v>41</v>
-      </c>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="39"/>
-      <c r="L3" s="39"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="26"/>
-      <c r="O3" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="P3" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q3" s="28"/>
-      <c r="R3" s="28"/>
-      <c r="S3" s="29"/>
-      <c r="T3" s="29"/>
-      <c r="U3" s="29"/>
-      <c r="V3" s="29"/>
-    </row>
-    <row r="4" spans="1:24" ht="19.5" customHeight="1" ns3:dyDescent="0.2">
-      <c r="A4" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="G4" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="H4" s="31" t="s">
-        <v>75</v>
-      </c>
-      <c r="I4"/>
-      <c r="J4" s="3"/>
-      <c r="O4" s="11"/>
-      <c r="P4" s="30"/>
-      <c r="S4" s="1"/>
-    </row>
-    <row r="5" spans="1:24" ht="6" customHeight="1" ns3:dyDescent="0.2"/>
-    <row r="6" spans="1:24" ht="15" customHeight="1" ns3:dyDescent="0.2">
+    <row r="1" spans="1:24" ht="24" customHeight="1" ns2:dyDescent="0.25">
+      <c r="A1" s="251" t="inlineStr">
+        <is>
+          <t>${competition.competitionName}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" spans="1:24" ht="24" customHeight="1" ns2:dyDescent="0.2">
+      <c r="A2" s="252" t="inlineStr">
+        <is>
+          <t>${t.get("Competition.competitionSite")} :</t>
+        </is>
+      </c>
+      <c r="D2" s="253" t="inlineStr">
+        <is>
+          <t>${competition.competitionSite}</t>
+        </is>
+      </c>
+      <c r="K2" s="254" t="inlineStr">
+        <is>
+          <t>${t.get("Competition.competitionCity")} :</t>
+        </is>
+      </c>
+      <c r="N2" s="255" t="inlineStr">
+        <is>
+          <t>${competition.competitionCity}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" spans="1:24" ht="24" customHeight="1" ns2:dyDescent="0.25">
+      <c r="A3" s="256" t="inlineStr">
+        <is>
+          <t>${t.get("Competition.competitionDate")} :</t>
+        </is>
+      </c>
+      <c r="D3" s="257" t="inlineStr">
+        <is>
+          <t>${competition.localizedCompetitionDate}</t>
+        </is>
+      </c>
+      <c r="K3" s="260" t="inlineStr">
+        <is>
+          <t>${t.get("Competition.competitionOrganizer")} :</t>
+        </is>
+      </c>
+      <c r="N3" s="259" t="inlineStr">
+        <is>
+          <t>${competition.competitionOrganizer}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" spans="1:24" ht="19.5" customHeight="1" ns2:dyDescent="0.2">
+      <c r="A4" s="261" t="inlineStr">
+        <is>
+          <t>${session != null ? t.get("Group") + " :" : ""}</t>
+        </is>
+      </c>
+      <c r="D4" s="257" t="inlineStr">
+        <is>
+          <t>${session != null ? session.name : ""}</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" spans="1:24" ht="6" customHeight="1" ns2:dyDescent="0.2"/>
+    <row r="6" spans="1:24" ht="15" customHeight="1" ns2:dyDescent="0.2">
       <c r="A6" s="105" t="s">
         <v>38</v>
       </c>
@@ -2980,7 +4476,7 @@
       <c r="V6" s="93"/>
       <c r="X6"/>
     </row>
-    <row r="7" spans="1:24" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.2">
+    <row r="7" spans="1:24" s="1" customFormat="1" ht="15" customHeight="1" ns2:dyDescent="0.2">
       <c r="A7" s="106"/>
       <c r="B7" s="106"/>
       <c r="C7" s="108"/>
@@ -3028,7 +4524,7 @@
       <c r="U7" s="94"/>
       <c r="V7" s="95"/>
     </row>
-    <row r="8" spans="1:24" s="10" customFormat="1" ht="7.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="8" spans="1:24" s="10" customFormat="1" ht="7.5" customHeight="1" ns2:dyDescent="0.2">
       <c r="A8" s="32"/>
       <c r="B8" s="32"/>
       <c r="C8" s="32"/>
@@ -3041,7 +4537,7 @@
       <c r="J8" s="33"/>
       <c r="K8" s="34"/>
     </row>
-    <row r="9" spans="1:24" ht="21.75" customHeight="1" ns3:dyDescent="0.2">
+    <row r="9" spans="1:24" ht="21.75" customHeight="1" ns2:dyDescent="0.2">
       <c r="A9" s="35" t="s">
         <v>47</v>
       </c>
@@ -3068,7 +4564,7 @@
       <c r="V9" s="38"/>
       <c r="X9"/>
     </row>
-    <row r="10" spans="1:24" s="10" customFormat="1" ht="21.2" customHeight="1" ns3:dyDescent="0.2">
+    <row r="10" spans="1:24" s="10" customFormat="1" ht="21.2" customHeight="1" ns2:dyDescent="0.2">
       <c r="A10" s="8" t="s">
         <v>1</v>
       </c>
@@ -3134,7 +4630,7 @@
       </c>
       <c r="V10" s="97"/>
     </row>
-    <row r="11" spans="1:24" ht="24.75" customHeight="1" ns3:dyDescent="0.2">
+    <row r="11" spans="1:24" ht="24.75" customHeight="1" ns2:dyDescent="0.2">
       <c r="B11"/>
       <c r="G11"/>
       <c r="H11"/>
@@ -3152,13 +4648,13 @@
       <c r="W11"/>
       <c r="X11"/>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="15" ns3:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="15" ns2:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>48</v>
       </c>
       <c r="J12" s="14"/>
     </row>
-    <row r="13" spans="1:24" s="13" customFormat="1" ht="6.75" customHeight="1" ns3:dyDescent="0.25">
+    <row r="13" spans="1:24" s="13" customFormat="1" ht="6.75" customHeight="1" ns2:dyDescent="0.25">
       <c r="A13" s="55"/>
       <c r="B13" s="55"/>
       <c r="C13" s="55"/>
@@ -3182,7 +4678,7 @@
       <c r="U13" s="56"/>
       <c r="V13" s="56"/>
     </row>
-    <row r="14" spans="1:24" s="66" customFormat="1" ht="12" ns3:dyDescent="0.2">
+    <row r="14" spans="1:24" s="66" customFormat="1" ht="12" ns2:dyDescent="0.2">
       <c r="A14" s="57" t="s">
         <v>49</v>
       </c>
@@ -3229,7 +4725,7 @@
       <c r="V14" s="65"/>
       <c r="X14" s="59"/>
     </row>
-    <row r="15" spans="1:24" s="74" customFormat="1" ns3:dyDescent="0.2">
+    <row r="15" spans="1:24" s="74" customFormat="1" ns2:dyDescent="0.2">
       <c r="A15" s="67" t="s">
         <v>57</v>
       </c>
@@ -3276,11 +4772,11 @@
       <c r="V15" s="69"/>
       <c r="X15" s="69"/>
     </row>
-    <row r="16" spans="1:24" ht="6" customHeight="1" ns3:dyDescent="0.2">
+    <row r="16" spans="1:24" ht="6" customHeight="1" ns2:dyDescent="0.2">
       <c r="C16" s="132"/>
       <c r="D16" s="132"/>
     </row>
-    <row r="17" spans="1:24" s="13" customFormat="1" ht="20.25" customHeight="1" ns3:dyDescent="0.2">
+    <row r="17" spans="1:24" s="13" customFormat="1" ht="20.25" customHeight="1" ns2:dyDescent="0.2">
       <c r="A17" s="133" t="s">
         <v>91</v>
       </c>
@@ -3320,7 +4816,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="16.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="18" spans="1:24" ht="16.5" customHeight="1" ns2:dyDescent="0.2">
       <c r="A18" s="133"/>
       <c r="B18" s="133"/>
       <c r="C18" s="142"/>
@@ -3349,7 +4845,7 @@
       <c r="V18" s="146"/>
       <c r="W18"/>
     </row>
-    <row r="19" spans="1:24" ns3:dyDescent="0.2">
+    <row r="19" spans="1:24" ns2:dyDescent="0.2">
       <c r="A19" s="147"/>
       <c r="B19" s="148"/>
       <c r="D19" s="147"/>
@@ -3372,7 +4868,7 @@
       <c r="V19" s="151"/>
       <c r="X19"/>
     </row>
-    <row r="20" spans="1:24" ht="13.7" customHeight="1" ns3:dyDescent="0.2">
+    <row r="20" spans="1:24" ht="13.7" customHeight="1" ns2:dyDescent="0.2">
       <c r="A20" s="147"/>
       <c r="B20" s="152" t="s">
         <v>70</v>
@@ -3409,7 +4905,7 @@
       <c r="V20" s="144"/>
       <c r="X20"/>
     </row>
-    <row r="21" spans="1:24" s="18" customFormat="1" ht="12.75" customHeight="1" ns3:dyDescent="0.2">
+    <row r="21" spans="1:24" s="18" customFormat="1" ht="12.75" customHeight="1" ns2:dyDescent="0.2">
       <c r="A21" s="154"/>
       <c r="B21" s="155"/>
       <c r="E21" s="156"/>
@@ -3419,7 +4915,7 @@
       <c r="Q21" s="154"/>
       <c r="V21" s="158"/>
     </row>
-    <row r="22" spans="1:24" ht="17.45" customHeight="1" ns3:dyDescent="0.2">
+    <row r="22" spans="1:24" ht="17.45" customHeight="1" ns2:dyDescent="0.2">
       <c r="A22" s="159" t="s">
         <v>72</v>
       </c>
@@ -3443,7 +4939,7 @@
       <c r="W22"/>
       <c r="X22"/>
     </row>
-    <row r="23" spans="1:24" ht="13.7" customHeight="1" ns3:dyDescent="0.2">
+    <row r="23" spans="1:24" ht="13.7" customHeight="1" ns2:dyDescent="0.2">
       <c r="A23" s="159"/>
       <c r="B23" s="159"/>
       <c r="C23" s="143" t="s">
@@ -3476,243 +4972,243 @@
       <c r="W23"/>
       <c r="X23"/>
     </row>
-    <row r="24" spans="1:24" ns3:dyDescent="0.2">
+    <row r="24" spans="1:24" ns2:dyDescent="0.2">
       <c r="F24" s="1"/>
     </row>
-    <row r="25" spans="1:24" ns3:dyDescent="0.2">
+    <row r="25" spans="1:24" ns2:dyDescent="0.2">
       <c r="F25" s="1"/>
     </row>
-    <row r="26" spans="1:24" ns3:dyDescent="0.2">
+    <row r="26" spans="1:24" ns2:dyDescent="0.2">
       <c r="F26" s="1"/>
     </row>
-    <row r="27" spans="1:24" ns3:dyDescent="0.2">
+    <row r="27" spans="1:24" ns2:dyDescent="0.2">
       <c r="F27" s="1"/>
     </row>
-    <row r="28" spans="1:24" ns3:dyDescent="0.2">
+    <row r="28" spans="1:24" ns2:dyDescent="0.2">
       <c r="F28" s="1"/>
     </row>
-    <row r="29" spans="1:24" ns3:dyDescent="0.2">
+    <row r="29" spans="1:24" ns2:dyDescent="0.2">
       <c r="F29" s="1"/>
     </row>
-    <row r="30" spans="1:24" ns3:dyDescent="0.2">
+    <row r="30" spans="1:24" ns2:dyDescent="0.2">
       <c r="F30" s="1"/>
     </row>
-    <row r="31" spans="1:24" ns3:dyDescent="0.2">
+    <row r="31" spans="1:24" ns2:dyDescent="0.2">
       <c r="F31" s="1"/>
     </row>
-    <row r="32" spans="1:24" ns3:dyDescent="0.2">
+    <row r="32" spans="1:24" ns2:dyDescent="0.2">
       <c r="F32" s="1"/>
     </row>
-    <row r="33" spans="6:6" ns3:dyDescent="0.2">
+    <row r="33" spans="6:6" ns2:dyDescent="0.2">
       <c r="F33" s="1"/>
     </row>
-    <row r="34" spans="6:6" ns3:dyDescent="0.2">
+    <row r="34" spans="6:6" ns2:dyDescent="0.2">
       <c r="F34" s="1"/>
     </row>
-    <row r="35" spans="6:6" ns3:dyDescent="0.2">
+    <row r="35" spans="6:6" ns2:dyDescent="0.2">
       <c r="F35" s="1"/>
     </row>
-    <row r="36" spans="6:6" ns3:dyDescent="0.2">
+    <row r="36" spans="6:6" ns2:dyDescent="0.2">
       <c r="F36" s="1"/>
     </row>
-    <row r="37" spans="6:6" ns3:dyDescent="0.2">
+    <row r="37" spans="6:6" ns2:dyDescent="0.2">
       <c r="F37" s="1"/>
     </row>
-    <row r="38" spans="6:6" ns3:dyDescent="0.2">
+    <row r="38" spans="6:6" ns2:dyDescent="0.2">
       <c r="F38" s="1"/>
     </row>
-    <row r="39" spans="6:6" ns3:dyDescent="0.2">
+    <row r="39" spans="6:6" ns2:dyDescent="0.2">
       <c r="F39" s="1"/>
     </row>
-    <row r="40" spans="6:6" ns3:dyDescent="0.2">
+    <row r="40" spans="6:6" ns2:dyDescent="0.2">
       <c r="F40" s="1"/>
     </row>
-    <row r="41" spans="6:6" ns3:dyDescent="0.2">
+    <row r="41" spans="6:6" ns2:dyDescent="0.2">
       <c r="F41" s="1"/>
     </row>
-    <row r="42" spans="6:6" ns3:dyDescent="0.2">
+    <row r="42" spans="6:6" ns2:dyDescent="0.2">
       <c r="F42" s="1"/>
     </row>
-    <row r="43" spans="6:6" ns3:dyDescent="0.2">
+    <row r="43" spans="6:6" ns2:dyDescent="0.2">
       <c r="F43" s="1"/>
     </row>
-    <row r="44" spans="6:6" ns3:dyDescent="0.2">
+    <row r="44" spans="6:6" ns2:dyDescent="0.2">
       <c r="F44" s="1"/>
     </row>
-    <row r="45" spans="6:6" ns3:dyDescent="0.2">
+    <row r="45" spans="6:6" ns2:dyDescent="0.2">
       <c r="F45" s="1"/>
     </row>
-    <row r="46" spans="6:6" ns3:dyDescent="0.2">
+    <row r="46" spans="6:6" ns2:dyDescent="0.2">
       <c r="F46" s="1"/>
     </row>
-    <row r="47" spans="6:6" ns3:dyDescent="0.2">
+    <row r="47" spans="6:6" ns2:dyDescent="0.2">
       <c r="F47" s="1"/>
     </row>
-    <row r="48" spans="6:6" ns3:dyDescent="0.2">
+    <row r="48" spans="6:6" ns2:dyDescent="0.2">
       <c r="F48" s="1"/>
     </row>
-    <row r="49" spans="6:6" ns3:dyDescent="0.2">
+    <row r="49" spans="6:6" ns2:dyDescent="0.2">
       <c r="F49" s="1"/>
     </row>
-    <row r="50" spans="6:6" ns3:dyDescent="0.2">
+    <row r="50" spans="6:6" ns2:dyDescent="0.2">
       <c r="F50" s="1"/>
     </row>
-    <row r="51" spans="6:6" ns3:dyDescent="0.2">
+    <row r="51" spans="6:6" ns2:dyDescent="0.2">
       <c r="F51" s="1"/>
     </row>
-    <row r="52" spans="6:6" ns3:dyDescent="0.2">
+    <row r="52" spans="6:6" ns2:dyDescent="0.2">
       <c r="F52" s="1"/>
     </row>
-    <row r="53" spans="6:6" ns3:dyDescent="0.2">
+    <row r="53" spans="6:6" ns2:dyDescent="0.2">
       <c r="F53" s="1"/>
     </row>
-    <row r="54" spans="6:6" ns3:dyDescent="0.2">
+    <row r="54" spans="6:6" ns2:dyDescent="0.2">
       <c r="F54" s="1"/>
     </row>
-    <row r="55" spans="6:6" ns3:dyDescent="0.2">
+    <row r="55" spans="6:6" ns2:dyDescent="0.2">
       <c r="F55" s="1"/>
     </row>
-    <row r="56" spans="6:6" ns3:dyDescent="0.2">
+    <row r="56" spans="6:6" ns2:dyDescent="0.2">
       <c r="F56" s="1"/>
     </row>
-    <row r="57" spans="6:6" ns3:dyDescent="0.2">
+    <row r="57" spans="6:6" ns2:dyDescent="0.2">
       <c r="F57" s="1"/>
     </row>
-    <row r="58" spans="6:6" ns3:dyDescent="0.2">
+    <row r="58" spans="6:6" ns2:dyDescent="0.2">
       <c r="F58" s="1"/>
     </row>
-    <row r="59" spans="6:6" ns3:dyDescent="0.2">
+    <row r="59" spans="6:6" ns2:dyDescent="0.2">
       <c r="F59" s="1"/>
     </row>
-    <row r="60" spans="6:6" ns3:dyDescent="0.2">
+    <row r="60" spans="6:6" ns2:dyDescent="0.2">
       <c r="F60" s="1"/>
     </row>
-    <row r="61" spans="6:6" ns3:dyDescent="0.2">
+    <row r="61" spans="6:6" ns2:dyDescent="0.2">
       <c r="F61" s="1"/>
     </row>
-    <row r="62" spans="6:6" ns3:dyDescent="0.2">
+    <row r="62" spans="6:6" ns2:dyDescent="0.2">
       <c r="F62" s="1"/>
     </row>
-    <row r="63" spans="6:6" ns3:dyDescent="0.2">
+    <row r="63" spans="6:6" ns2:dyDescent="0.2">
       <c r="F63" s="1"/>
     </row>
-    <row r="64" spans="6:6" ns3:dyDescent="0.2">
+    <row r="64" spans="6:6" ns2:dyDescent="0.2">
       <c r="F64" s="1"/>
     </row>
-    <row r="65" spans="6:6" ns3:dyDescent="0.2">
+    <row r="65" spans="6:6" ns2:dyDescent="0.2">
       <c r="F65" s="1"/>
     </row>
-    <row r="66" spans="6:6" ns3:dyDescent="0.2">
+    <row r="66" spans="6:6" ns2:dyDescent="0.2">
       <c r="F66" s="1"/>
     </row>
-    <row r="67" spans="6:6" ns3:dyDescent="0.2">
+    <row r="67" spans="6:6" ns2:dyDescent="0.2">
       <c r="F67" s="1"/>
     </row>
-    <row r="68" spans="6:6" ns3:dyDescent="0.2">
+    <row r="68" spans="6:6" ns2:dyDescent="0.2">
       <c r="F68" s="1"/>
     </row>
-    <row r="69" spans="6:6" ns3:dyDescent="0.2">
+    <row r="69" spans="6:6" ns2:dyDescent="0.2">
       <c r="F69" s="1"/>
     </row>
-    <row r="70" spans="6:6" ns3:dyDescent="0.2">
+    <row r="70" spans="6:6" ns2:dyDescent="0.2">
       <c r="F70" s="1"/>
     </row>
-    <row r="71" spans="6:6" ns3:dyDescent="0.2">
+    <row r="71" spans="6:6" ns2:dyDescent="0.2">
       <c r="F71" s="1"/>
     </row>
-    <row r="72" spans="6:6" ns3:dyDescent="0.2">
+    <row r="72" spans="6:6" ns2:dyDescent="0.2">
       <c r="F72" s="1"/>
     </row>
-    <row r="73" spans="6:6" ns3:dyDescent="0.2">
+    <row r="73" spans="6:6" ns2:dyDescent="0.2">
       <c r="F73" s="1"/>
     </row>
-    <row r="74" spans="6:6" ns3:dyDescent="0.2">
+    <row r="74" spans="6:6" ns2:dyDescent="0.2">
       <c r="F74" s="1"/>
     </row>
-    <row r="75" spans="6:6" ns3:dyDescent="0.2">
+    <row r="75" spans="6:6" ns2:dyDescent="0.2">
       <c r="F75" s="1"/>
     </row>
-    <row r="76" spans="6:6" ns3:dyDescent="0.2">
+    <row r="76" spans="6:6" ns2:dyDescent="0.2">
       <c r="F76" s="1"/>
     </row>
-    <row r="77" spans="6:6" ns3:dyDescent="0.2">
+    <row r="77" spans="6:6" ns2:dyDescent="0.2">
       <c r="F77" s="1"/>
     </row>
-    <row r="78" spans="6:6" ns3:dyDescent="0.2">
+    <row r="78" spans="6:6" ns2:dyDescent="0.2">
       <c r="F78" s="1"/>
     </row>
-    <row r="79" spans="6:6" ns3:dyDescent="0.2">
+    <row r="79" spans="6:6" ns2:dyDescent="0.2">
       <c r="F79" s="1"/>
     </row>
-    <row r="80" spans="6:6" ns3:dyDescent="0.2">
+    <row r="80" spans="6:6" ns2:dyDescent="0.2">
       <c r="F80" s="1"/>
     </row>
-    <row r="81" spans="6:6" ns3:dyDescent="0.2">
+    <row r="81" spans="6:6" ns2:dyDescent="0.2">
       <c r="F81" s="1"/>
     </row>
-    <row r="82" spans="6:6" ns3:dyDescent="0.2">
+    <row r="82" spans="6:6" ns2:dyDescent="0.2">
       <c r="F82" s="1"/>
     </row>
-    <row r="83" spans="6:6" ns3:dyDescent="0.2">
+    <row r="83" spans="6:6" ns2:dyDescent="0.2">
       <c r="F83" s="1"/>
     </row>
-    <row r="84" spans="6:6" ns3:dyDescent="0.2">
+    <row r="84" spans="6:6" ns2:dyDescent="0.2">
       <c r="F84" s="1"/>
     </row>
-    <row r="85" spans="6:6" ns3:dyDescent="0.2">
+    <row r="85" spans="6:6" ns2:dyDescent="0.2">
       <c r="F85" s="1"/>
     </row>
-    <row r="86" spans="6:6" ns3:dyDescent="0.2">
+    <row r="86" spans="6:6" ns2:dyDescent="0.2">
       <c r="F86" s="1"/>
     </row>
-    <row r="87" spans="6:6" ns3:dyDescent="0.2">
+    <row r="87" spans="6:6" ns2:dyDescent="0.2">
       <c r="F87" s="1"/>
     </row>
-    <row r="88" spans="6:6" ns3:dyDescent="0.2">
+    <row r="88" spans="6:6" ns2:dyDescent="0.2">
       <c r="F88" s="1"/>
     </row>
-    <row r="89" spans="6:6" ns3:dyDescent="0.2">
+    <row r="89" spans="6:6" ns2:dyDescent="0.2">
       <c r="F89" s="1"/>
     </row>
-    <row r="90" spans="6:6" ns3:dyDescent="0.2">
+    <row r="90" spans="6:6" ns2:dyDescent="0.2">
       <c r="F90" s="1"/>
     </row>
-    <row r="91" spans="6:6" ns3:dyDescent="0.2">
+    <row r="91" spans="6:6" ns2:dyDescent="0.2">
       <c r="F91" s="1"/>
     </row>
-    <row r="92" spans="6:6" ns3:dyDescent="0.2">
+    <row r="92" spans="6:6" ns2:dyDescent="0.2">
       <c r="F92" s="1"/>
     </row>
-    <row r="93" spans="6:6" ns3:dyDescent="0.2">
+    <row r="93" spans="6:6" ns2:dyDescent="0.2">
       <c r="F93" s="1"/>
     </row>
-    <row r="94" spans="6:6" ns3:dyDescent="0.2">
+    <row r="94" spans="6:6" ns2:dyDescent="0.2">
       <c r="F94" s="1"/>
     </row>
-    <row r="95" spans="6:6" ns3:dyDescent="0.2">
+    <row r="95" spans="6:6" ns2:dyDescent="0.2">
       <c r="F95" s="1"/>
     </row>
-    <row r="96" spans="6:6" ns3:dyDescent="0.2">
+    <row r="96" spans="6:6" ns2:dyDescent="0.2">
       <c r="F96" s="1"/>
     </row>
-    <row r="97" spans="6:6" ns3:dyDescent="0.2">
+    <row r="97" spans="6:6" ns2:dyDescent="0.2">
       <c r="F97" s="1"/>
     </row>
-    <row r="98" spans="6:6" ns3:dyDescent="0.2">
+    <row r="98" spans="6:6" ns2:dyDescent="0.2">
       <c r="F98" s="1"/>
     </row>
-    <row r="99" spans="6:6" ns3:dyDescent="0.2">
+    <row r="99" spans="6:6" ns2:dyDescent="0.2">
       <c r="F99" s="1"/>
     </row>
-    <row r="100" spans="6:6" ns3:dyDescent="0.2">
+    <row r="100" spans="6:6" ns2:dyDescent="0.2">
       <c r="F100" s="1"/>
     </row>
-    <row r="101" spans="6:6" ns3:dyDescent="0.2">
+    <row r="101" spans="6:6" ns2:dyDescent="0.2">
       <c r="F101" s="1"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <mergeCells count="24">
+  <mergeCells count="34">
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="C6:C7"/>
@@ -3723,7 +5219,6 @@
     <mergeCell ref="H6:H7"/>
     <mergeCell ref="I6:M6"/>
     <mergeCell ref="N6:R6"/>
-    <mergeCell ref="H1:V1"/>
     <mergeCell ref="U6:V7"/>
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="S6:T6"/>
@@ -3737,6 +5232,17 @@
     <mergeCell ref="Q17:R18"/>
     <mergeCell ref="Q19:R20"/>
     <mergeCell ref="Q22:R23"/>
+    <mergeCell ref="A1:V1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="D2:J2"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="N2:V2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:J3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="N3:V3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:V4"/>
   </mergeCells>
   <conditionalFormatting sqref="D8">
     <cfRule type="expression" dxfId="1" priority="8" stopIfTrue="1">
@@ -3749,23 +5255,20 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation showErrorMessage="1" sqref="H4 F23 C20 C17 S17 L17 F17 F20 C23 L20 S20 S23" ns2:uid="{00000000-0002-0000-0000-000000000000}"/>
-    <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" sqref="F10 H11:H13" ns2:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation showErrorMessage="1" sqref="H4 F23 C20 C17 S17 L17 F17 F20 C23 L20 S20 S23" ns1:uid="{00000000-0002-0000-0000-000000000000}"/>
+    <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" sqref="F10 H11:H13" ns1:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>0</formula1>
       <formula2>200</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I8" ns2:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I8" ns1:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>0</formula1>
       <formula2>200</formula2>
     </dataValidation>
   </dataValidations>
-  <hyperlinks>
-    <hyperlink ref="A3" ns4:id="rId1" display="www.federation.org" ns2:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="A4" ns4:id="rId2" display="records@federation.org" ns2:uid="{00000000-0004-0000-0000-000001000000}"/>
-  </hyperlinks>
+  <hyperlinks/>
   <pageMargins left="0.31496062992125984" right="0.35433070866141736" top="0.39370078740157483" bottom="0.47244094488188981" header="0.51181102362204722" footer="0.23622047244094491"/>
-  <pageSetup paperSize="9" scale="60" firstPageNumber="0" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" ns4:id="rId3"/>
+  <pageSetup paperSize="9" scale="60" firstPageNumber="0" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" ns3:id="rId3"/>
   <headerFooter alignWithMargins="0"/>
-  <legacyDrawing ns4:id="rId4"/>
+  <legacyDrawing ns3:id="rId4"/>
 </worksheet>
 </file>